--- a/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
+++ b/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I710"/>
+  <dimension ref="A1:I711"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24128,6 +24128,43 @@
         </is>
       </c>
     </row>
+    <row r="711">
+      <c r="A711" t="n">
+        <v>775</v>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>844 021</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>15.09.2026</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Za jízdy občas nasvítí N2, vyměnili pouze snímač směrového válce mechaniku nechali</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr"/>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>Spalovací motor / Pohon</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr"/>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>Radek</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>Radek</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
+++ b/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I711"/>
+  <dimension ref="A1:I712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24165,6 +24165,47 @@
         </is>
       </c>
     </row>
+    <row r="712">
+      <c r="A712" t="n">
+        <v>776</v>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>844 015</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Nedobíjí B, podle kódu blikající LED přehřátí generátoru (otrokovice)</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>v depu oprava konektoru pod velkým deklem generátoru C1-C2 měli 125 Ohm</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>Dobíjení</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr"/>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>Radek</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>Radek</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
+++ b/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I712"/>
+  <dimension ref="A1:I713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24206,6 +24206,43 @@
         </is>
       </c>
     </row>
+    <row r="713">
+      <c r="A713" t="n">
+        <v>777</v>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>844 015</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>20.09.2026</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Červený alarm motoru B v SAMu hlásí alarm teploty vyšší jak 105 stupňů ,motorari vyměnili chladič a termostat</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr"/>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>Spalovací motor / Pohon</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr"/>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>Radek</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>Radek</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
+++ b/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I713"/>
+  <dimension ref="A1:I714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24243,6 +24243,43 @@
         </is>
       </c>
     </row>
+    <row r="714">
+      <c r="A714" t="n">
+        <v>778</v>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>844 014</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Bez komunikace CPU1, firovi stopovala mašina ,výměna  zdrojovky a CPU1</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr"/>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>Elektrická výzbroj</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr"/>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>Radek</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>Radek</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
+++ b/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I714"/>
+  <dimension ref="A1:I715"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24280,6 +24280,43 @@
         </is>
       </c>
     </row>
+    <row r="715">
+      <c r="A715" t="n">
+        <v>779</v>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>844 025</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>22.09.2026</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Výměna jízdní páky na B , nešla potvrdit do výkonu</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr"/>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>Elektrická výzbroj</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr"/>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>Radek</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>Radek</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
+++ b/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I715"/>
+  <dimension ref="A1:I716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24317,6 +24317,43 @@
         </is>
       </c>
     </row>
+    <row r="716">
+      <c r="A716" t="n">
+        <v>780</v>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>844 028</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Vadný požární kabel na motoru B, upadl chladič taky na B - oprava konektoru pro zobrazovače AD-Blue</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr"/>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>Elektrická výzbroj</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr"/>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>Radek</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>Radek</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
+++ b/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I716"/>
+  <dimension ref="A1:I717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24354,6 +24354,47 @@
         </is>
       </c>
     </row>
+    <row r="717">
+      <c r="A717" t="n">
+        <v>781</v>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>844 028</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>04.10.2026</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Vadny pozarni kabel na B motore. Vymena za  novy.</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>Pouzilibjsme je 13,5 m</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>Elektrická výzbroj</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr"/>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>Petr</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>Petr</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
+++ b/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I717"/>
+  <dimension ref="A1:I718"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24395,6 +24395,47 @@
         </is>
       </c>
     </row>
+    <row r="718">
+      <c r="A718" t="n">
+        <v>782</v>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>844 028</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>04.10.2026</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Vadny pozarni kabel na B motore. Vymena za  novy.</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>Pouzilibjsme je 13,5 m</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>Elektrická výzbroj</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr"/>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>Petr</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>Petr</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
+++ b/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I718"/>
+  <dimension ref="A1:I717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24395,47 +24395,6 @@
         </is>
       </c>
     </row>
-    <row r="718">
-      <c r="A718" t="n">
-        <v>782</v>
-      </c>
-      <c r="B718" t="inlineStr">
-        <is>
-          <t>844 028</t>
-        </is>
-      </c>
-      <c r="C718" t="inlineStr">
-        <is>
-          <t>04.10.2026</t>
-        </is>
-      </c>
-      <c r="D718" t="inlineStr">
-        <is>
-          <t>Vadny pozarni kabel na B motore. Vymena za  novy.</t>
-        </is>
-      </c>
-      <c r="E718" t="inlineStr">
-        <is>
-          <t>Pouzilibjsme je 13,5 m</t>
-        </is>
-      </c>
-      <c r="F718" t="inlineStr">
-        <is>
-          <t>Elektrická výzbroj</t>
-        </is>
-      </c>
-      <c r="G718" t="inlineStr"/>
-      <c r="H718" t="inlineStr">
-        <is>
-          <t>Petr</t>
-        </is>
-      </c>
-      <c r="I718" t="inlineStr">
-        <is>
-          <t>Petr</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
+++ b/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I717"/>
+  <dimension ref="A1:I718"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24395,6 +24395,43 @@
         </is>
       </c>
     </row>
+    <row r="718">
+      <c r="A718" t="n">
+        <v>782</v>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>844 021</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>05.10.2026</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Výměna náhonu ETCS 2 osa č.1</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr"/>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>Elektrická výzbroj</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr"/>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>Radek</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>Radek</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
+++ b/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I718"/>
+  <dimension ref="A1:I719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24432,6 +24432,47 @@
         </is>
       </c>
     </row>
+    <row r="719">
+      <c r="A719" t="n">
+        <v>783</v>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>814 063</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>08.10.2026</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Výměna displeje Lokel na 814</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>Použity z 814 028 po vyhoření</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>Elektrická výzbroj</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr"/>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>Radek</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>Radek</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
+++ b/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I719"/>
+  <dimension ref="A1:I720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24473,6 +24473,47 @@
         </is>
       </c>
     </row>
+    <row r="720">
+      <c r="A720" t="n">
+        <v>784</v>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>844 003</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>22.10.2026</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Na A levé dveře při zavření dveří stále svítí tlačitka otevření a osvětlení nástupního protoru, zjištěn zkrat mezi vodiči 810 a 824, nad dveřma je odpojený vodič 824</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>Chtělo by to až bude odstavena projít ještě výdejní okno jestli to tam není někde propojené</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>Elektrická výzbroj</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr"/>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>Radek</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>Radek</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
+++ b/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I720"/>
+  <dimension ref="A1:I721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24514,6 +24514,43 @@
         </is>
       </c>
     </row>
+    <row r="721">
+      <c r="A721" t="n">
+        <v>785</v>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>844 003</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>22.10.2026</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Při snížení slaku o 1 bar se nasvítí kontrolka plnění 5 barů, zjištěn rozepnutý prostřední podvozek SP18.2 - výměna</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr"/>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>Elektrická výzbroj</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr"/>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>Radek</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>Radek</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
+++ b/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
@@ -24530,7 +24530,7 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>Při snížení slaku o 1 bar se nasvítí kontrolka plnění 5 barů, zjištěn rozepnutý prostřední podvozek SP18.2 - výměna</t>
+          <t>Při snížení tlaku o 1 bar se nasvítí kontrolka plnění 5 barů, zjištěn rozepnutý prostřední podvozek SP18.2 - výměna</t>
         </is>
       </c>
       <c r="E721" t="inlineStr"/>

--- a/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
+++ b/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I721"/>
+  <dimension ref="A1:I722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24551,6 +24551,43 @@
         </is>
       </c>
     </row>
+    <row r="722">
+      <c r="A722" t="n">
+        <v>786</v>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>842 010</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>23.10.2026</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Nejde odvetravani ETCS skrine. Provizorne dosazen ventilator s mensim vykonem. Az se tu ukaze vymenit na original</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr"/>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>VZ - Radiostanice</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr"/>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>Petr</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>Petr</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
+++ b/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I722"/>
+  <dimension ref="A1:I723"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24588,6 +24588,47 @@
         </is>
       </c>
     </row>
+    <row r="723">
+      <c r="A723" t="n">
+        <v>787</v>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>844 020</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Vypadává směr na A</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>Prověření linky od směrového válce do konektoru SAM- OK -&gt; přehození SAMů mezi sebou (A&lt;-&gt;B)</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>Spalovací motor / Pohon</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr"/>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>Dan</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>Dan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
+++ b/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I723"/>
+  <dimension ref="A1:I724"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24629,6 +24629,47 @@
         </is>
       </c>
     </row>
+    <row r="724">
+      <c r="A724" t="n">
+        <v>788</v>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>814 002</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Opakovaně se samovolně restartuje, jedna nebo druhá půlka infosystému.</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>IS se nerozpadl - nedelano (za mě OK)</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>IS - Infosystém</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr"/>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>Dan</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>Dan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
+++ b/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I724"/>
+  <dimension ref="A1:J724"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,11 @@
           <t>Upravil</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Sledováno</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -495,6 +500,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -528,6 +536,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -565,6 +576,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -598,6 +612,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -631,6 +648,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -664,6 +684,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -701,6 +724,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -734,6 +760,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -771,6 +800,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -808,6 +840,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -845,6 +880,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -882,6 +920,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -919,6 +960,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -952,6 +996,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -989,6 +1036,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1022,6 +1072,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1055,6 +1108,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1088,6 +1144,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1121,6 +1180,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1158,6 +1220,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1191,6 +1256,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1224,6 +1292,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1261,6 +1332,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1294,6 +1368,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1331,6 +1408,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1368,6 +1448,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1401,6 +1484,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1438,6 +1524,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1471,6 +1560,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1508,6 +1600,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1545,6 +1640,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1582,6 +1680,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1615,6 +1716,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1648,6 +1752,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1685,6 +1792,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1718,6 +1828,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J37" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1755,6 +1868,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J38" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1792,6 +1908,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J39" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1825,6 +1944,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J40" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1862,6 +1984,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J41" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1899,6 +2024,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1936,6 +2064,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J43" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1969,6 +2100,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2006,6 +2140,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J45" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2039,6 +2176,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J46" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2076,6 +2216,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J47" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2113,6 +2256,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2150,6 +2296,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J49" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2187,6 +2336,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2224,6 +2376,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2261,6 +2416,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2298,6 +2456,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2335,6 +2496,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2368,6 +2532,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2405,6 +2572,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2438,6 +2608,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2475,6 +2648,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2508,6 +2684,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2545,6 +2724,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2582,6 +2764,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2619,6 +2804,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2656,6 +2844,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J63" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2693,6 +2884,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J64" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2730,6 +2924,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J65" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2767,6 +2964,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2804,6 +3004,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J67" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2837,6 +3040,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J68" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2874,6 +3080,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J69" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2911,6 +3120,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J70" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2948,6 +3160,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J71" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2985,6 +3200,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3018,6 +3236,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3051,6 +3272,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3088,6 +3312,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3121,6 +3348,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3150,6 +3380,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3187,6 +3420,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3220,6 +3456,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -3257,6 +3496,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -3290,6 +3532,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -3319,6 +3564,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J82" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -3348,6 +3596,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3381,6 +3632,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J84" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3414,6 +3668,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3451,6 +3708,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J86" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -3484,6 +3744,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J87" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -3517,6 +3780,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J88" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -3554,6 +3820,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J89" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -3587,6 +3856,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J90" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -3616,6 +3888,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J91" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -3649,6 +3924,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J92" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -3686,6 +3964,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J93" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -3719,6 +4000,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J94" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -3752,6 +4036,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J95" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -3789,6 +4076,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J96" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -3822,6 +4112,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J97" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -3855,6 +4148,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J98" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -3892,6 +4188,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J99" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -3929,6 +4228,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J100" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -3962,6 +4264,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J101" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -3991,6 +4296,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J102" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -4028,6 +4336,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J103" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -4065,6 +4376,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J104" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -4098,6 +4412,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J105" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -4127,6 +4444,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J106" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -4156,6 +4476,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J107" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -4193,6 +4516,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J108" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -4230,6 +4556,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J109" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -4267,6 +4596,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J110" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -4296,6 +4628,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J111" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -4329,6 +4664,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J112" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -4358,6 +4696,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J113" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -4387,6 +4728,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J114" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -4416,6 +4760,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J115" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -4449,6 +4796,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J116" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -4482,6 +4832,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J117" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -4511,6 +4864,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J118" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -4540,6 +4896,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J119" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -4569,6 +4928,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J120" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -4598,6 +4960,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J121" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -4631,6 +4996,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J122" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -4664,6 +5032,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J123" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -4701,6 +5072,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J124" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -4734,6 +5108,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J125" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -4771,6 +5148,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J126" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -4808,6 +5188,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J127" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -4837,6 +5220,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J128" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -4866,6 +5252,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J129" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -4903,6 +5292,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J130" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -4940,6 +5332,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J131" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -4977,6 +5372,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J132" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -5014,6 +5412,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J133" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -5047,6 +5448,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J134" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -5076,6 +5480,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J135" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -5109,6 +5516,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J136" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -5142,6 +5552,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J137" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -5179,6 +5592,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J138" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -5212,6 +5628,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J139" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -5245,6 +5664,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J140" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -5278,6 +5700,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J141" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -5311,6 +5736,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J142" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -5344,6 +5772,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J143" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -5377,6 +5808,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J144" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -5410,6 +5844,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J145" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -5439,6 +5876,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J146" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -5472,6 +5912,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J147" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -5505,6 +5948,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J148" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -5542,6 +5988,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J149" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -5579,6 +6028,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J150" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -5612,6 +6064,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J151" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -5649,6 +6104,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J152" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -5686,6 +6144,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J153" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -5715,6 +6176,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J154" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -5748,6 +6212,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J155" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -5781,6 +6248,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J156" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -5814,6 +6284,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J157" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -5851,6 +6324,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J158" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -5888,6 +6364,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J159" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -5925,6 +6404,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J160" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -5954,6 +6436,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J161" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -5987,6 +6472,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J162" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -6020,6 +6508,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J163" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -6057,6 +6548,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J164" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -6090,6 +6584,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J165" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -6123,6 +6620,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J166" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -6156,6 +6656,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J167" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -6193,6 +6696,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J168" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -6230,6 +6736,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J169" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -6263,6 +6772,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J170" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -6300,6 +6812,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J171" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -6333,6 +6848,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J172" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -6366,6 +6884,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J173" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -6399,6 +6920,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J174" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -6432,6 +6956,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J175" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -6461,6 +6988,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J176" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -6494,6 +7024,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J177" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -6523,6 +7056,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J178" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -6560,6 +7096,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J179" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -6597,6 +7136,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J180" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -6630,6 +7172,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J181" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -6663,6 +7208,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J182" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -6692,6 +7240,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J183" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -6725,6 +7276,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J184" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -6758,6 +7312,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J185" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -6795,6 +7352,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J186" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -6828,6 +7388,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J187" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -6861,6 +7424,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J188" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -6898,6 +7464,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J189" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -6931,6 +7500,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J190" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -6964,6 +7536,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J191" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -6997,6 +7572,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J192" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -7026,6 +7604,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J193" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -7055,6 +7636,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J194" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -7088,6 +7672,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J195" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -7121,6 +7708,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J196" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -7154,6 +7744,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J197" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -7191,6 +7784,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J198" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -7228,6 +7824,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J199" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -7265,6 +7864,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J200" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -7298,6 +7900,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J201" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -7331,6 +7936,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J202" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -7368,6 +7976,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J203" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -7405,6 +8016,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J204" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -7442,6 +8056,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J205" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -7475,6 +8092,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J206" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -7508,6 +8128,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J207" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -7541,6 +8164,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J208" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -7574,6 +8200,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J209" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -7607,6 +8236,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J210" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -7640,6 +8272,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J211" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -7669,6 +8304,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J212" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -7698,6 +8336,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J213" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -7731,6 +8372,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J214" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -7764,6 +8408,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J215" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -7793,6 +8440,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J216" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -7822,6 +8472,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J217" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -7851,6 +8504,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J218" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -7880,6 +8536,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J219" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -7909,6 +8568,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J220" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -7942,6 +8604,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J221" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -7971,6 +8636,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J222" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -8000,6 +8668,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J223" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -8033,6 +8704,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J224" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -8062,6 +8736,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J225" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -8095,6 +8772,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J226" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -8124,6 +8804,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J227" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -8153,6 +8836,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J228" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -8186,6 +8872,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J229" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -8219,6 +8908,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J230" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -8252,6 +8944,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J231" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -8285,6 +8980,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J232" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -8318,6 +9016,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J233" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -8351,6 +9052,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J234" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -8384,6 +9088,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J235" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -8417,6 +9124,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J236" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -8450,6 +9160,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J237" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -8487,6 +9200,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J238" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -8520,6 +9236,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J239" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -8557,6 +9276,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J240" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -8590,6 +9312,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J241" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -8623,6 +9348,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J242" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -8656,6 +9384,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J243" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -8689,6 +9420,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J244" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -8722,6 +9456,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J245" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -8751,6 +9488,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J246" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -8784,6 +9524,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J247" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -8817,6 +9560,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J248" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -8850,6 +9596,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J249" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -8883,6 +9632,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J250" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -8912,6 +9664,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J251" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -8945,6 +9700,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J252" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -8978,6 +9736,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J253" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -9007,6 +9768,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J254" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -9040,6 +9804,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J255" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -9077,6 +9844,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J256" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -9114,6 +9884,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J257" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -9143,6 +9916,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J258" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -9176,6 +9952,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J259" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -9209,6 +9988,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J260" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -9242,6 +10024,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J261" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -9275,6 +10060,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J262" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -9308,6 +10096,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J263" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -9337,6 +10128,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J264" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -9366,6 +10160,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J265" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -9395,6 +10192,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J266" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -9424,6 +10224,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J267" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -9453,6 +10256,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J268" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -9486,6 +10292,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J269" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -9519,6 +10328,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J270" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -9552,6 +10364,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J271" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -9585,6 +10400,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J272" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -9618,6 +10436,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J273" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -9647,6 +10468,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J274" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -9680,6 +10504,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J275" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -9713,6 +10540,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J276" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -9746,6 +10576,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J277" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -9779,6 +10612,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J278" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -9812,6 +10648,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J279" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -9845,6 +10684,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J280" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -9878,6 +10720,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J281" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -9911,6 +10756,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J282" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -9944,6 +10792,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J283" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -9977,6 +10828,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J284" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -10006,6 +10860,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J285" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -10039,6 +10896,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J286" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -10068,6 +10928,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J287" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -10101,6 +10964,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J288" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -10130,6 +10996,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J289" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -10159,6 +11028,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J290" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -10188,6 +11060,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J291" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -10221,6 +11096,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J292" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -10254,6 +11132,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J293" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -10283,6 +11164,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J294" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -10312,6 +11196,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J295" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -10341,6 +11228,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J296" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -10370,6 +11260,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J297" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -10399,6 +11292,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J298" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -10428,6 +11324,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J299" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -10457,6 +11356,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J300" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -10486,6 +11388,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J301" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -10515,6 +11420,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J302" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -10544,6 +11452,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J303" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -10577,6 +11488,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J304" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -10610,6 +11524,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J305" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -10639,6 +11556,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J306" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -10668,6 +11588,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J307" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -10697,6 +11620,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J308" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -10726,6 +11652,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J309" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -10755,6 +11684,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J310" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -10784,6 +11716,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J311" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -10813,6 +11748,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J312" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -10846,6 +11784,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J313" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -10879,6 +11820,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J314" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -10912,6 +11856,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J315" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -10945,6 +11892,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J316" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -10978,6 +11928,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J317" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -11011,6 +11964,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J318" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -11044,6 +12000,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J319" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -11081,6 +12040,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J320" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -11114,6 +12076,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J321" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -11147,6 +12112,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J322" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -11180,6 +12148,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J323" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -11213,6 +12184,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J324" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -11246,6 +12220,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J325" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -11279,6 +12256,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J326" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -11308,6 +12288,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J327" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -11341,6 +12324,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J328" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -11374,6 +12360,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J329" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -11407,6 +12396,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J330" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -11440,6 +12432,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J331" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -11477,6 +12472,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J332" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -11506,6 +12504,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J333" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -11543,6 +12544,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J334" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -11576,6 +12580,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J335" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -11609,6 +12616,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J336" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -11642,6 +12652,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J337" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -11675,6 +12688,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J338" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -11708,6 +12724,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J339" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -11741,6 +12760,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J340" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -11774,6 +12796,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J341" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -11807,6 +12832,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J342" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -11840,6 +12868,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J343" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -11873,6 +12904,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J344" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -11910,6 +12944,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J345" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -11947,6 +12984,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J346" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -11984,6 +13024,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J347" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -12021,6 +13064,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J348" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -12058,6 +13104,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J349" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -12091,6 +13140,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J350" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -12124,6 +13176,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J351" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -12161,6 +13216,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J352" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -12198,6 +13256,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J353" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -12235,6 +13296,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J354" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -12272,6 +13336,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J355" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -12301,6 +13368,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J356" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -12334,6 +13404,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J357" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -12367,6 +13440,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J358" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -12400,6 +13476,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J359" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -12433,6 +13512,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J360" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -12462,6 +13544,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J361" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -12495,6 +13580,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J362" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -12528,6 +13616,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J363" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -12561,6 +13652,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J364" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -12594,6 +13688,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J365" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -12627,6 +13724,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J366" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -12660,6 +13760,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J367" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -12689,6 +13792,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J368" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -12718,6 +13824,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J369" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -12755,6 +13864,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J370" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -12788,6 +13900,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J371" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -12821,6 +13936,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J372" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -12858,6 +13976,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J373" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -12895,6 +14016,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J374" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -12928,6 +14052,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J375" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -12961,6 +14088,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J376" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -12998,6 +14128,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J377" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -13031,6 +14164,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J378" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -13064,6 +14200,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J379" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -13097,6 +14236,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J380" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -13130,6 +14272,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J381" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -13163,6 +14308,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J382" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -13196,6 +14344,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J383" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -13225,6 +14376,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J384" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -13258,6 +14412,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J385" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -13291,6 +14448,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J386" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -13324,6 +14484,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J387" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -13361,6 +14524,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J388" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -13398,6 +14564,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J389" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -13435,6 +14604,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J390" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -13472,6 +14644,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J391" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -13501,6 +14676,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J392" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -13534,6 +14712,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J393" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -13563,6 +14744,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J394" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -13596,6 +14780,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J395" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -13629,6 +14816,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J396" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -13662,6 +14852,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J397" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -13695,6 +14888,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J398" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -13728,6 +14924,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J399" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -13761,6 +14960,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J400" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -13794,6 +14996,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J401" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -13827,6 +15032,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J402" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -13860,6 +15068,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J403" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -13893,6 +15104,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J404" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -13922,6 +15136,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J405" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -13955,6 +15172,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J406" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -13988,6 +15208,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J407" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -14021,6 +15244,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J408" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -14054,6 +15280,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J409" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -14083,6 +15312,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J410" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -14116,6 +15348,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J411" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -14149,6 +15384,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J412" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -14178,6 +15416,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J413" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -14211,6 +15452,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J414" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -14244,6 +15488,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J415" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -14277,6 +15524,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J416" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -14310,6 +15560,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J417" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -14343,6 +15596,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J418" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -14376,6 +15632,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J419" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -14409,6 +15668,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J420" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -14442,6 +15704,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J421" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -14475,6 +15740,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J422" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -14508,6 +15776,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J423" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -14541,6 +15812,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J424" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -14574,6 +15848,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J425" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -14607,6 +15884,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J426" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -14640,6 +15920,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J427" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -14677,6 +15960,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J428" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -14714,6 +16000,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J429" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -14751,6 +16040,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J430" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -14788,6 +16080,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J431" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -14825,6 +16120,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J432" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -14862,6 +16160,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J433" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -14899,6 +16200,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J434" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -14936,6 +16240,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J435" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -14973,6 +16280,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J436" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -15010,6 +16320,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J437" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -15047,6 +16360,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J438" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -15080,6 +16396,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J439" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -15117,6 +16436,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J440" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -15154,6 +16476,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J441" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -15191,6 +16516,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J442" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -15228,6 +16556,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J443" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -15265,6 +16596,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J444" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -15302,6 +16636,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J445" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -15339,6 +16676,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J446" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -15376,6 +16716,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J447" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -15409,6 +16752,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J448" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -15442,6 +16788,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J449" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -15475,6 +16824,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J450" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -15508,6 +16860,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J451" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -15545,6 +16900,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J452" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -15578,6 +16936,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J453" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -15611,6 +16972,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J454" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -15648,6 +17012,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J455" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -15681,6 +17048,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J456" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -15714,6 +17084,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J457" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -15747,6 +17120,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J458" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -15780,6 +17156,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J459" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -15813,6 +17192,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J460" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -15850,6 +17232,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J461" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -15887,6 +17272,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J462" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -15916,6 +17304,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J463" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -15949,6 +17340,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J464" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -15982,6 +17376,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J465" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -16015,6 +17412,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J466" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -16044,6 +17444,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J467" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -16073,6 +17476,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J468" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -16102,6 +17508,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J469" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -16135,6 +17544,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J470" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -16164,6 +17576,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J471" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -16193,6 +17608,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J472" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -16222,6 +17640,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J473" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -16255,6 +17676,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J474" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -16288,6 +17712,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J475" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -16321,6 +17748,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J476" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -16350,6 +17780,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J477" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -16383,6 +17816,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J478" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -16412,6 +17848,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J479" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -16441,6 +17880,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J480" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -16470,6 +17912,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J481" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -16503,6 +17948,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J482" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -16536,6 +17984,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J483" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -16565,6 +18016,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J484" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -16594,6 +18048,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J485" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -16623,6 +18080,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J486" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -16656,6 +18116,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J487" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -16689,6 +18152,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J488" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -16722,6 +18188,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J489" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -16759,6 +18228,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J490" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -16796,6 +18268,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J491" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -16833,6 +18308,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J492" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -16866,6 +18344,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J493" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -16903,6 +18384,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J494" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -16936,6 +18420,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J495" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -16973,6 +18460,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J496" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -17006,6 +18496,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J497" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -17043,6 +18536,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J498" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -17076,6 +18572,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J499" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -17109,6 +18608,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J500" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -17146,6 +18648,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J501" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -17183,6 +18688,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J502" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -17220,6 +18728,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J503" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -17257,6 +18768,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J504" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -17294,6 +18808,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J505" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -17327,6 +18844,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J506" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -17364,6 +18884,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J507" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -17401,6 +18924,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J508" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -17438,6 +18964,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J509" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -17475,6 +19004,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J510" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -17508,6 +19040,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J511" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -17541,6 +19076,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J512" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -17578,6 +19116,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J513" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -17615,6 +19156,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J514" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -17652,6 +19196,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J515" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -17689,6 +19236,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J516" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -17726,6 +19276,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J517" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -17763,6 +19316,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J518" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -17800,6 +19356,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J519" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -17833,6 +19392,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J520" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -17866,6 +19428,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J521" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -17899,6 +19464,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J522" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -17932,6 +19500,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J523" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -17965,6 +19536,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J524" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -17998,6 +19572,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J525" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -18031,6 +19608,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J526" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -18064,6 +19644,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J527" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -18093,6 +19676,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J528" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -18126,6 +19712,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J529" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -18159,6 +19748,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J530" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -18192,6 +19784,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J531" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -18225,6 +19820,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J532" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -18258,6 +19856,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J533" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -18291,6 +19892,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J534" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -18324,6 +19928,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J535" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -18353,6 +19960,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J536" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -18386,6 +19996,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J537" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -18419,6 +20032,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J538" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -18452,6 +20068,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J539" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -18485,6 +20104,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J540" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -18518,6 +20140,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J541" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -18547,6 +20172,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J542" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -18584,6 +20212,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J543" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -18617,6 +20248,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J544" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -18650,6 +20284,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J545" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -18683,6 +20320,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J546" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -18716,6 +20356,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J547" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -18749,6 +20392,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J548" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -18782,6 +20428,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J549" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -18815,6 +20464,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J550" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -18848,6 +20500,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J551" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -18881,6 +20536,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J552" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -18914,6 +20572,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J553" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -18947,6 +20608,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J554" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -18980,6 +20644,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J555" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -19013,6 +20680,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J556" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -19046,6 +20716,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J557" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
@@ -19079,6 +20752,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J558" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
@@ -19112,6 +20788,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J559" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
@@ -19145,6 +20824,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J560" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
@@ -19178,6 +20860,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J561" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
@@ -19211,6 +20896,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J562" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -19244,6 +20932,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J563" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -19277,6 +20968,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J564" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -19310,6 +21004,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J565" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -19343,6 +21040,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J566" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -19376,6 +21076,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J567" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -19409,6 +21112,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J568" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
@@ -19442,6 +21148,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J569" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
@@ -19475,6 +21184,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J570" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -19508,6 +21220,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J571" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -19545,6 +21260,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J572" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
@@ -19582,6 +21300,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J573" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -19615,6 +21336,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J574" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -19648,6 +21372,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J575" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -19685,6 +21412,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J576" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
@@ -19722,6 +21452,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J577" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
@@ -19759,6 +21492,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J578" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
@@ -19796,6 +21532,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J579" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -19833,6 +21572,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J580" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
@@ -19870,6 +21612,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J581" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
@@ -19907,6 +21652,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J582" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -19944,6 +21692,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J583" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
@@ -19977,6 +21728,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J584" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -20014,6 +21768,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J585" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
@@ -20047,6 +21804,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J586" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
@@ -20076,6 +21836,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J587" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
@@ -20105,6 +21868,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J588" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
@@ -20134,6 +21900,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J589" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
@@ -20167,6 +21936,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J590" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
@@ -20200,6 +21972,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J591" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
@@ -20229,6 +22004,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J592" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
@@ -20262,6 +22040,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J593" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
@@ -20295,6 +22076,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J594" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
@@ -20328,6 +22112,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J595" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
@@ -20357,6 +22144,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J596" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
@@ -20386,6 +22176,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J597" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
@@ -20415,6 +22208,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J598" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
@@ -20448,6 +22244,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J599" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
@@ -20481,6 +22280,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J600" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
@@ -20514,6 +22316,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J601" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
@@ -20543,6 +22348,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J602" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
@@ -20576,6 +22384,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J603" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
@@ -20609,6 +22420,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J604" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
@@ -20642,6 +22456,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J605" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="n">
@@ -20671,6 +22488,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J606" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
@@ -20704,6 +22524,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J607" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="n">
@@ -20733,6 +22556,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J608" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
@@ -20762,6 +22588,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J609" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
@@ -20791,6 +22620,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J610" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="n">
@@ -20828,6 +22660,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J611" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="n">
@@ -20861,6 +22696,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J612" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="n">
@@ -20898,6 +22736,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J613" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
@@ -20931,6 +22772,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J614" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
@@ -20964,6 +22808,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J615" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="n">
@@ -20997,6 +22844,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J616" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
@@ -21030,6 +22880,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J617" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="n">
@@ -21067,6 +22920,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J618" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
@@ -21104,6 +22960,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J619" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
@@ -21137,6 +22996,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J620" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
@@ -21170,6 +23032,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J621" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
@@ -21203,6 +23068,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J622" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="n">
@@ -21232,6 +23100,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J623" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
@@ -21269,6 +23140,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J624" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="n">
@@ -21306,6 +23180,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J625" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="n">
@@ -21339,6 +23216,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J626" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
@@ -21372,6 +23252,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J627" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="n">
@@ -21405,6 +23288,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J628" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
@@ -21438,6 +23324,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J629" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="n">
@@ -21475,6 +23364,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J630" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="n">
@@ -21508,6 +23400,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J631" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="n">
@@ -21544,6 +23439,9 @@
         <is>
           <t>Radek</t>
         </is>
+      </c>
+      <c r="J632" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="633">
@@ -21570,6 +23468,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J633" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="n">
@@ -21599,6 +23500,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J634" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="n">
@@ -21628,6 +23532,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J635" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="n">
@@ -21657,6 +23564,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J636" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="n">
@@ -21690,6 +23600,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J637" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="n">
@@ -21719,6 +23632,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J638" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="n">
@@ -21748,6 +23664,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J639" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="n">
@@ -21777,6 +23696,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J640" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="n">
@@ -21810,6 +23732,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J641" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="n">
@@ -21843,6 +23768,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J642" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="n">
@@ -21876,6 +23804,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J643" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="n">
@@ -21909,6 +23840,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J644" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="n">
@@ -21942,6 +23876,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J645" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="n">
@@ -21979,6 +23916,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J646" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="n">
@@ -22016,6 +23956,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J647" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="n">
@@ -22049,6 +23992,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J648" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="n">
@@ -22082,6 +24028,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J649" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="n">
@@ -22111,6 +24060,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J650" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="n">
@@ -22140,6 +24092,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J651" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="n">
@@ -22173,6 +24128,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J652" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="n">
@@ -22202,6 +24160,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J653" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="n">
@@ -22231,6 +24192,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J654" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="n">
@@ -22264,6 +24228,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J655" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="n">
@@ -22293,6 +24260,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J656" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="n">
@@ -22326,6 +24296,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J657" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="n">
@@ -22355,6 +24328,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J658" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="n">
@@ -22384,6 +24360,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J659" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="n">
@@ -22417,6 +24396,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J660" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="n">
@@ -22450,6 +24432,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J661" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="n">
@@ -22483,6 +24468,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J662" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="n">
@@ -22512,6 +24500,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J663" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="n">
@@ -22545,6 +24536,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J664" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="n">
@@ -22578,6 +24572,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J665" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="n">
@@ -22607,6 +24604,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J666" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="n">
@@ -22636,6 +24636,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J667" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="n">
@@ -22669,6 +24672,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J668" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="n">
@@ -22702,6 +24708,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J669" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="n">
@@ -22735,6 +24744,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J670" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="n">
@@ -22764,6 +24776,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J671" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="n">
@@ -22797,6 +24812,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J672" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="n">
@@ -22826,6 +24844,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J673" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="n">
@@ -22855,6 +24876,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J674" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="n">
@@ -22884,6 +24908,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J675" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="n">
@@ -22913,6 +24940,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J676" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="n">
@@ -22946,6 +24976,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J677" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="n">
@@ -22975,6 +25008,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J678" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="n">
@@ -23004,6 +25040,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J679" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="n">
@@ -23037,6 +25076,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J680" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="n">
@@ -23066,6 +25108,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J681" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="n">
@@ -23095,6 +25140,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J682" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="n">
@@ -23128,6 +25176,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J683" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="n">
@@ -23165,6 +25216,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J684" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="n">
@@ -23202,6 +25256,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J685" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="n">
@@ -23239,6 +25296,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J686" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="n">
@@ -23272,6 +25332,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J687" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="n">
@@ -23305,6 +25368,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J688" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="n">
@@ -23338,6 +25404,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J689" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="n">
@@ -23371,6 +25440,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J690" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="n">
@@ -23408,6 +25480,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J691" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="n">
@@ -23445,6 +25520,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J692" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="n">
@@ -23482,6 +25560,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J693" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="n">
@@ -23519,6 +25600,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J694" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="n">
@@ -23552,6 +25636,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J695" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="n">
@@ -23589,6 +25676,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J696" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="n">
@@ -23622,6 +25712,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J697" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="n">
@@ -23663,6 +25756,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J698" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="n">
@@ -23700,6 +25796,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J699" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="n">
@@ -23741,6 +25840,9 @@
           <t>Petr</t>
         </is>
       </c>
+      <c r="J700" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="n">
@@ -23782,6 +25884,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J701" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="n">
@@ -23819,6 +25924,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J702" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="n">
@@ -23856,6 +25964,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J703" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="n">
@@ -23893,6 +26004,9 @@
           <t>Dan</t>
         </is>
       </c>
+      <c r="J704" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="n">
@@ -23934,6 +26048,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J705" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="n">
@@ -23971,6 +26088,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J706" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="n">
@@ -24012,6 +26132,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J707" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="n">
@@ -24049,6 +26172,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J708" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="n">
@@ -24090,6 +26216,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J709" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="n">
@@ -24127,6 +26256,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J710" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="n">
@@ -24164,6 +26296,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J711" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="n">
@@ -24205,6 +26340,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J712" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="n">
@@ -24242,6 +26380,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J713" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="n">
@@ -24279,6 +26420,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J714" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="n">
@@ -24316,6 +26460,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J715" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="n">
@@ -24353,6 +26500,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J716" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="n">
@@ -24394,6 +26544,9 @@
           <t>Petr</t>
         </is>
       </c>
+      <c r="J717" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="n">
@@ -24431,6 +26584,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J718" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="n">
@@ -24472,6 +26628,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J719" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="n">
@@ -24513,6 +26672,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J720" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="n">
@@ -24550,6 +26712,9 @@
           <t>Radek</t>
         </is>
       </c>
+      <c r="J721" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="n">
@@ -24587,6 +26752,9 @@
           <t>Petr</t>
         </is>
       </c>
+      <c r="J722" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="723">
       <c r="A723" t="n">
@@ -24628,6 +26796,9 @@
           <t>Dan</t>
         </is>
       </c>
+      <c r="J723" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="724">
       <c r="A724" t="n">
@@ -24668,6 +26839,9 @@
         <is>
           <t>Dan</t>
         </is>
+      </c>
+      <c r="J724" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
+++ b/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
@@ -26749,11 +26749,11 @@
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>Petr</t>
+          <t>Radek</t>
         </is>
       </c>
       <c r="J722" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="723">

--- a/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
+++ b/PREDAVKA_ELEKTRONICI_PRO_APPSHEET.xlsx
@@ -26793,11 +26793,11 @@
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Radek</t>
         </is>
       </c>
       <c r="J723" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="724">
